--- a/Entrevistas/Entrevistas_preenchidas.xlsx
+++ b/Entrevistas/Entrevistas_preenchidas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Mestrado\Materiais\_Artigos\Aprendizagem ativa em IoT - Uma abordagem baseada em pesquisa experimental e prototipação maker\Entrevistas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F3BDB3C-9C1E-4BE4-ADA2-C0674786E033}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCFD43E4-E2AB-44CD-8295-4A8D404DBC46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -357,6 +357,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -366,11 +371,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -550,7 +550,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="12"/>
@@ -614,7 +614,7 @@
       <c r="E6" s="13"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="9" t="s">
+      <c r="A8" s="6" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -631,7 +631,7 @@
       </c>
     </row>
     <row r="9" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="10"/>
+      <c r="A9" s="7"/>
       <c r="B9" s="4">
         <v>1</v>
       </c>
@@ -641,12 +641,12 @@
       <c r="D9" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E9" s="6">
-        <v>2</v>
+      <c r="E9" s="9">
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="10"/>
+      <c r="A10" s="7"/>
       <c r="B10" s="4">
         <v>2</v>
       </c>
@@ -656,10 +656,10 @@
       <c r="D10" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E10" s="7"/>
+      <c r="E10" s="10"/>
     </row>
     <row r="11" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A11" s="10"/>
+      <c r="A11" s="7"/>
       <c r="B11" s="4">
         <v>3</v>
       </c>
@@ -669,10 +669,10 @@
       <c r="D11" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E11" s="7"/>
+      <c r="E11" s="10"/>
     </row>
     <row r="12" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A12" s="10"/>
+      <c r="A12" s="7"/>
       <c r="B12" s="4">
         <v>4</v>
       </c>
@@ -682,10 +682,10 @@
       <c r="D12" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E12" s="7"/>
+      <c r="E12" s="10"/>
     </row>
     <row r="13" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A13" s="11"/>
+      <c r="A13" s="8"/>
       <c r="B13" s="4">
         <v>5</v>
       </c>
@@ -695,13 +695,13 @@
       <c r="D13" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E13" s="8"/>
+      <c r="E13" s="11"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B14" s="3"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="9" t="s">
+      <c r="A15" s="6" t="s">
         <v>19</v>
       </c>
       <c r="B15" s="1" t="s">
@@ -718,7 +718,7 @@
       </c>
     </row>
     <row r="16" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A16" s="10"/>
+      <c r="A16" s="7"/>
       <c r="B16" s="4">
         <v>1</v>
       </c>
@@ -728,12 +728,12 @@
       <c r="D16" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="E16" s="6">
-        <v>2</v>
+      <c r="E16" s="9">
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A17" s="10"/>
+      <c r="A17" s="7"/>
       <c r="B17" s="4">
         <v>2</v>
       </c>
@@ -743,10 +743,10 @@
       <c r="D17" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E17" s="7"/>
+      <c r="E17" s="10"/>
     </row>
     <row r="18" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A18" s="10"/>
+      <c r="A18" s="7"/>
       <c r="B18" s="4">
         <v>3</v>
       </c>
@@ -756,10 +756,10 @@
       <c r="D18" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E18" s="7"/>
+      <c r="E18" s="10"/>
     </row>
     <row r="19" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A19" s="10"/>
+      <c r="A19" s="7"/>
       <c r="B19" s="4">
         <v>4</v>
       </c>
@@ -769,10 +769,10 @@
       <c r="D19" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E19" s="7"/>
+      <c r="E19" s="10"/>
     </row>
     <row r="20" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A20" s="11"/>
+      <c r="A20" s="8"/>
       <c r="B20" s="4">
         <v>5</v>
       </c>
@@ -782,13 +782,13 @@
       <c r="D20" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="E20" s="8"/>
+      <c r="E20" s="11"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B21" s="3"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="9" t="s">
+      <c r="A22" s="6" t="s">
         <v>30</v>
       </c>
       <c r="B22" s="1" t="s">
@@ -805,7 +805,7 @@
       </c>
     </row>
     <row r="23" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="10"/>
+      <c r="A23" s="7"/>
       <c r="B23" s="4">
         <v>1</v>
       </c>
@@ -815,12 +815,12 @@
       <c r="D23" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="E23" s="6">
-        <v>3</v>
+      <c r="E23" s="9">
+        <v>4</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="10"/>
+      <c r="A24" s="7"/>
       <c r="B24" s="4">
         <v>2</v>
       </c>
@@ -830,10 +830,10 @@
       <c r="D24" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="E24" s="7"/>
+      <c r="E24" s="10"/>
     </row>
     <row r="25" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A25" s="10"/>
+      <c r="A25" s="7"/>
       <c r="B25" s="4">
         <v>3</v>
       </c>
@@ -843,10 +843,10 @@
       <c r="D25" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="E25" s="7"/>
+      <c r="E25" s="10"/>
     </row>
     <row r="26" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A26" s="10"/>
+      <c r="A26" s="7"/>
       <c r="B26" s="4">
         <v>4</v>
       </c>
@@ -856,10 +856,10 @@
       <c r="D26" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="E26" s="7"/>
+      <c r="E26" s="10"/>
     </row>
     <row r="27" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="11"/>
+      <c r="A27" s="8"/>
       <c r="B27" s="4">
         <v>5</v>
       </c>
@@ -869,13 +869,13 @@
       <c r="D27" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="E27" s="8"/>
+      <c r="E27" s="11"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B28" s="3"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="9" t="s">
+      <c r="A29" s="6" t="s">
         <v>41</v>
       </c>
       <c r="B29" s="1" t="s">
@@ -892,7 +892,7 @@
       </c>
     </row>
     <row r="30" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A30" s="10"/>
+      <c r="A30" s="7"/>
       <c r="B30" s="4">
         <v>1</v>
       </c>
@@ -902,12 +902,12 @@
       <c r="D30" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E30" s="6">
-        <v>3</v>
+      <c r="E30" s="9">
+        <v>4</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="10"/>
+      <c r="A31" s="7"/>
       <c r="B31" s="4">
         <v>2</v>
       </c>
@@ -917,10 +917,10 @@
       <c r="D31" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="E31" s="7"/>
+      <c r="E31" s="10"/>
     </row>
     <row r="32" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A32" s="10"/>
+      <c r="A32" s="7"/>
       <c r="B32" s="4">
         <v>3</v>
       </c>
@@ -930,10 +930,10 @@
       <c r="D32" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="E32" s="7"/>
+      <c r="E32" s="10"/>
     </row>
     <row r="33" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A33" s="10"/>
+      <c r="A33" s="7"/>
       <c r="B33" s="4">
         <v>4</v>
       </c>
@@ -943,10 +943,10 @@
       <c r="D33" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="E33" s="7"/>
+      <c r="E33" s="10"/>
     </row>
     <row r="34" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="11"/>
+      <c r="A34" s="8"/>
       <c r="B34" s="4">
         <v>5</v>
       </c>
@@ -956,13 +956,13 @@
       <c r="D34" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="E34" s="8"/>
+      <c r="E34" s="11"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B35" s="3"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A36" s="9" t="s">
+      <c r="A36" s="6" t="s">
         <v>52</v>
       </c>
       <c r="B36" s="1" t="s">
@@ -979,7 +979,7 @@
       </c>
     </row>
     <row r="37" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A37" s="10"/>
+      <c r="A37" s="7"/>
       <c r="B37" s="4">
         <v>1</v>
       </c>
@@ -989,12 +989,12 @@
       <c r="D37" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E37" s="6">
-        <v>3</v>
+      <c r="E37" s="9">
+        <v>4</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A38" s="10"/>
+      <c r="A38" s="7"/>
       <c r="B38" s="4">
         <v>2</v>
       </c>
@@ -1004,10 +1004,10 @@
       <c r="D38" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="E38" s="7"/>
+      <c r="E38" s="10"/>
     </row>
     <row r="39" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A39" s="10"/>
+      <c r="A39" s="7"/>
       <c r="B39" s="4">
         <v>3</v>
       </c>
@@ -1017,10 +1017,10 @@
       <c r="D39" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="E39" s="7"/>
+      <c r="E39" s="10"/>
     </row>
     <row r="40" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A40" s="10"/>
+      <c r="A40" s="7"/>
       <c r="B40" s="4">
         <v>4</v>
       </c>
@@ -1030,10 +1030,10 @@
       <c r="D40" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="E40" s="7"/>
+      <c r="E40" s="10"/>
     </row>
     <row r="41" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A41" s="11"/>
+      <c r="A41" s="8"/>
       <c r="B41" s="4">
         <v>5</v>
       </c>
@@ -1043,13 +1043,13 @@
       <c r="D41" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="E41" s="8"/>
+      <c r="E41" s="11"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B42" s="3"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A43" s="9" t="s">
+      <c r="A43" s="6" t="s">
         <v>63</v>
       </c>
       <c r="B43" s="1" t="s">
@@ -1066,7 +1066,7 @@
       </c>
     </row>
     <row r="44" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A44" s="10"/>
+      <c r="A44" s="7"/>
       <c r="B44" s="4">
         <v>1</v>
       </c>
@@ -1076,12 +1076,12 @@
       <c r="D44" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="E44" s="6">
-        <v>2</v>
+      <c r="E44" s="9">
+        <v>3</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A45" s="10"/>
+      <c r="A45" s="7"/>
       <c r="B45" s="4">
         <v>2</v>
       </c>
@@ -1091,10 +1091,10 @@
       <c r="D45" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="E45" s="7"/>
+      <c r="E45" s="10"/>
     </row>
     <row r="46" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A46" s="10"/>
+      <c r="A46" s="7"/>
       <c r="B46" s="4">
         <v>3</v>
       </c>
@@ -1104,10 +1104,10 @@
       <c r="D46" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="E46" s="7"/>
+      <c r="E46" s="10"/>
     </row>
     <row r="47" spans="1:5" ht="72" x14ac:dyDescent="0.3">
-      <c r="A47" s="10"/>
+      <c r="A47" s="7"/>
       <c r="B47" s="4">
         <v>4</v>
       </c>
@@ -1117,10 +1117,10 @@
       <c r="D47" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E47" s="7"/>
+      <c r="E47" s="10"/>
     </row>
     <row r="48" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A48" s="11"/>
+      <c r="A48" s="8"/>
       <c r="B48" s="4">
         <v>5</v>
       </c>
@@ -1130,16 +1130,10 @@
       <c r="D48" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="E48" s="8"/>
+      <c r="E48" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A22:A27"/>
-    <mergeCell ref="A15:A20"/>
-    <mergeCell ref="E37:E41"/>
-    <mergeCell ref="E44:E48"/>
-    <mergeCell ref="A29:A34"/>
-    <mergeCell ref="A43:A48"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A36:A41"/>
     <mergeCell ref="B2:E2"/>
@@ -1152,6 +1146,12 @@
     <mergeCell ref="E23:E27"/>
     <mergeCell ref="E30:E34"/>
     <mergeCell ref="A8:A13"/>
+    <mergeCell ref="A22:A27"/>
+    <mergeCell ref="A15:A20"/>
+    <mergeCell ref="E37:E41"/>
+    <mergeCell ref="E44:E48"/>
+    <mergeCell ref="A29:A34"/>
+    <mergeCell ref="A43:A48"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
